--- a/Results/LICALS_vs_MND_LICALS.xlsx
+++ b/Results/LICALS_vs_MND_LICALS.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>LICALS</t>
+          <t>RILUZOLE PLACEBO</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>MND LICALS</t>
+          <t>RILUZOLE MND</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -468,16 +468,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>58.66 ± 10.80</t>
+          <t>56.00 ± 11.55</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>57.10 ± 12.34</t>
+          <t>57.90 ± 9.81</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2343</v>
+        <v>0.0756</v>
       </c>
     </row>
     <row r="3">
@@ -493,12 +493,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16.32 ± 4.96</t>
+          <t>0.11 ± 0.23</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.30 ± 5.35</t>
+          <t>11.81 ± 7.13</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -519,7 +519,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.2102</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -535,12 +535,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50 (29.1%)</t>
+          <t>89 (37.4%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>53 (36.3%)</t>
+          <t>63 (37.3%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -558,12 +558,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>122 (70.9%)</t>
+          <t>149 (62.6%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>93 (63.7%)</t>
+          <t>106 (62.7%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -582,7 +582,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>0.0451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -598,12 +598,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>32 (18.6%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>42 (28.8%)</t>
+          <t>53 (31.4%)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -621,12 +621,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>140 (81.4%)</t>
+          <t>238 (100.0%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>104 (71.2%)</t>
+          <t>116 (68.6%)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>

--- a/Results/LICALS_vs_MND_LICALS.xlsx
+++ b/Results/LICALS_vs_MND_LICALS.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>RILUZOLE PLACEBO</t>
+          <t>LICALS PLACEBO</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>RILUZOLE MND</t>
+          <t>LICALS MND</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -468,16 +468,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>56.00 ± 11.55</t>
+          <t>58.74 ± 10.10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>57.90 ± 9.81</t>
+          <t>57.10 ± 12.34</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0756</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="3">
@@ -493,12 +493,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.11 ± 0.23</t>
+          <t>16.57 ± 4.47</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.81 ± 7.13</t>
+          <t>9.30 ± 5.35</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -519,7 +519,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.6214</v>
       </c>
     </row>
     <row r="5">
@@ -535,12 +535,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>89 (37.4%)</t>
+          <t>27 (32.1%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>63 (37.3%)</t>
+          <t>53 (36.3%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -558,12 +558,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>149 (62.6%)</t>
+          <t>57 (67.9%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>106 (62.7%)</t>
+          <t>93 (63.7%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -582,7 +582,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.0917</v>
       </c>
     </row>
     <row r="8">
@@ -598,12 +598,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>15 (17.9%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>53 (31.4%)</t>
+          <t>42 (28.8%)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -621,12 +621,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>238 (100.0%)</t>
+          <t>69 (82.1%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>116 (68.6%)</t>
+          <t>104 (71.2%)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
